--- a/example/option_files/example_database_options.xlsx
+++ b/example/option_files/example_database_options.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19280" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="signals" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="loops" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="signals" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="loops" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -539,7 +539,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>philips_waves</t>
+          <t>other::waves</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -557,7 +557,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>philips_waves</t>
+          <t>other::waves</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>philips_waves</t>
+          <t>other::waves</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>philips_waves</t>
+          <t>other::waves</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -652,7 +652,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>philips_waves</t>
+          <t>other::waves</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>philips_waves</t>
+          <t>other::waves</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>philips_numerics</t>
+          <t>other::numerics</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>philips_numerics</t>
+          <t>other::numerics</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>philips_numerics</t>
+          <t>other::numerics</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>philips_numerics</t>
+          <t>other::numerics</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -817,44 +817,38 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>syringe</t>
+          <t>other::syringe</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vitesse Babynoradrenaline</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>µg/h</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>5</v>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>eit</t>
+          <t>other::syringe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Europe/Paris</t>
-        </is>
+          <t>Vitesse Babynoradrenaline</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>µg/h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -865,22 +859,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Ohms</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>black</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Impedance value; Impedance</t>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
@@ -892,7 +882,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Local 1*</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -902,12 +892,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>black</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Impedance value</t>
+          <t>Impedance value; Impedance</t>
         </is>
       </c>
     </row>
@@ -919,7 +909,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Local 2*</t>
+          <t>Local 1*</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -929,7 +919,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>red</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -946,7 +936,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Local 3*</t>
+          <t>Local 2*</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -956,7 +946,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -973,7 +963,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Local 4*</t>
+          <t>Local 3*</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -983,7 +973,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>green</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1000,33 +990,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>%Local 1*</t>
+          <t>Local 4*</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Proportion</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.05</v>
+          <t>Ohms</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>purple</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Impedance</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>fraction</t>
+          <t>Impedance value</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1017,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>%Local 2*</t>
+          <t>%Local 1*</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1046,9 +1025,15 @@
           <t>Proportion</t>
         </is>
       </c>
+      <c r="F20" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.05</v>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>red</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1058,7 +1043,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>fraction</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1055,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>%Local 3*</t>
+          <t>%Local 2*</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1080,12 +1065,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>Impedance</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>percentage</t>
         </is>
       </c>
     </row>
@@ -1097,20 +1087,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>%Local 3*</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Proportion</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Impedance</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>eit</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>%Local 4*</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Proportion</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>purple</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Impedance</t>
         </is>
@@ -1159,7 +1176,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>philips_waves</t>
+          <t>other::waves</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
